--- a/artfynd/A 49494-2019 artfynd.xlsx
+++ b/artfynd/A 49494-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121467775</v>
       </c>
       <c r="B2" t="n">
-        <v>98011</v>
+        <v>98012</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -770,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Camilla Ährlund, Sofia Fast</t>
+          <t>Sofia Fast, Camilla Ährlund</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">

--- a/artfynd/A 49494-2019 artfynd.xlsx
+++ b/artfynd/A 49494-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121467775</v>
       </c>
       <c r="B2" t="n">
-        <v>98012</v>
+        <v>98015</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -770,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Sofia Fast, Camilla Ährlund</t>
+          <t>Camilla Ährlund, Sofia Fast</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">

--- a/artfynd/A 49494-2019 artfynd.xlsx
+++ b/artfynd/A 49494-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121467775</v>
       </c>
       <c r="B2" t="n">
-        <v>98015</v>
+        <v>98021</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 49494-2019 artfynd.xlsx
+++ b/artfynd/A 49494-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121467775</v>
       </c>
       <c r="B2" t="n">
-        <v>98021</v>
+        <v>98022</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -770,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Camilla Ährlund, Sofia Fast</t>
+          <t>Sofia Fast, Camilla Ährlund</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">

--- a/artfynd/A 49494-2019 artfynd.xlsx
+++ b/artfynd/A 49494-2019 artfynd.xlsx
@@ -770,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Sofia Fast, Camilla Ährlund</t>
+          <t>Camilla Ährlund, Sofia Fast</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">

--- a/artfynd/A 49494-2019 artfynd.xlsx
+++ b/artfynd/A 49494-2019 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121467775</v>
       </c>
       <c r="B2" t="n">
-        <v>98022</v>
+        <v>98030</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
